--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1357,68 +1357,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1357,68 +1357,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU7"/>
+  <dimension ref="A1:AU8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,109 +1520,268 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="3" t="n">
+        <v>46176.875</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ethiopia Ethiopia Premier League</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Welayta Dicha</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Negele Arsi Ketema</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AF8" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" s="3" t="n">
+      <c r="AJ8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="3" t="n">
         <v>46176.875</v>
       </c>
     </row>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>1.67</v>
       </c>
       <c r="O8" t="n">
-        <v>2.34</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.95</v>
+        <v>4.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.72</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.6</v>
       </c>
-      <c r="S8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.39</v>
+        <v>1.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.49</v>
+        <v>2.44</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1357,68 +1357,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>2.34</v>
       </c>
       <c r="P6" t="n">
-        <v>4.38</v>
+        <v>2.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>3.72</v>
       </c>
       <c r="R6" t="n">
-        <v>2.48</v>
+        <v>1.6</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="T6" t="n">
-        <v>3.45</v>
+        <v>1.87</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.58</v>
+        <v>1.15</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>2.39</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.44</v>
+        <v>1.49</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1357,68 +1357,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1205,10 +1205,10 @@
         <v>1.4</v>
       </c>
       <c r="O5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P5" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q5" t="n">
         <v>1.89</v>
@@ -1217,28 +1217,28 @@
         <v>2.48</v>
       </c>
       <c r="S5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T5" t="n">
         <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W5" t="n">
         <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AA5" t="n">
         <v>1.41</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>2.34</v>
       </c>
       <c r="P8" t="n">
-        <v>4.38</v>
+        <v>2.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>3.72</v>
       </c>
       <c r="R8" t="n">
-        <v>2.48</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="T8" t="n">
-        <v>3.45</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.58</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.5</v>
+        <v>2.39</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.44</v>
+        <v>1.49</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.61</v>
+        <v>4.06</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>1.71</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>1.61</v>
       </c>
       <c r="O8" t="n">
-        <v>2.34</v>
+        <v>3.9</v>
       </c>
       <c r="P8" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.72</v>
+        <v>2.18</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="S8" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>3.55</v>
       </c>
       <c r="U8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.15</v>
+        <v>1.62</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.76</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.98</v>
+        <v>4.85</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.24</v>
+        <v>1.53</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.06</v>
+        <v>1.54</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.39</v>
+        <v>1.51</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.49</v>
+        <v>2.36</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.36</v>
+        <v>1.99</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU8"/>
+  <dimension ref="A1:AU7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>1.61</v>
       </c>
       <c r="O7" t="n">
-        <v>2.37</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.64</v>
+        <v>2.18</v>
       </c>
       <c r="R7" t="n">
-        <v>1.74</v>
+        <v>2.4</v>
       </c>
       <c r="S7" t="n">
-        <v>1.74</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U7" t="n">
         <v>2.1</v>
       </c>
-      <c r="U7" t="n">
-        <v>4.23</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.78</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>2</v>
+        <v>4.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.75</v>
+        <v>1.53</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.06</v>
+        <v>1.54</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.64</v>
+        <v>1.51</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.45</v>
+        <v>2.36</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.42</v>
+        <v>1.99</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1623,165 +1623,6 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46176.875</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>46176</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Real Potosí</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" s="3" t="n">
         <v>46176.875</v>
       </c>
     </row>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.06</v>
+        <v>1.61</v>
       </c>
       <c r="O6" t="n">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.71</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.61</v>
+        <v>4.06</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>1.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1208,7 +1208,7 @@
         <v>4.4</v>
       </c>
       <c r="P5" t="n">
-        <v>6.25</v>
+        <v>5.81</v>
       </c>
       <c r="Q5" t="n">
         <v>1.89</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.61</v>
+        <v>3.95</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>1.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.18</v>
+        <v>4.56</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="V6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.62</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AG6" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.99</v>
+        <v>1.16</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.06</v>
+        <v>1.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.95</v>
+        <v>1.61</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.72</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.56</v>
+        <v>2.18</v>
       </c>
       <c r="R6" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="U6" t="n">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.05</v>
+        <v>4.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.16</v>
+        <v>1.99</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.61</v>
+        <v>3.95</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.18</v>
+        <v>4.56</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="V7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.62</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AG7" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.99</v>
+        <v>1.16</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1205,31 +1205,31 @@
         <v>1.4</v>
       </c>
       <c r="O5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P5" t="n">
         <v>5.81</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="R5" t="n">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="S5" t="n">
         <v>1.2</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U5" t="n">
         <v>2.1</v>
       </c>
       <c r="V5" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
@@ -1241,25 +1241,25 @@
         <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.52</v>
+        <v>2.73</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AE5" t="n">
         <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.61</v>
+        <v>4.06</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>1.71</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.18</v>
+        <v>4.56</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="V6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.62</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AG6" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.99</v>
+        <v>1.16</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.95</v>
+        <v>1.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>1.72</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.56</v>
+        <v>2.18</v>
       </c>
       <c r="R7" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="U7" t="n">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.05</v>
+        <v>4.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.16</v>
+        <v>1.99</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.06</v>
+        <v>1.61</v>
       </c>
       <c r="O6" t="n">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.71</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.56</v>
+        <v>2.18</v>
       </c>
       <c r="R6" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="U6" t="n">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.05</v>
+        <v>4.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.16</v>
+        <v>1.99</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.61</v>
+        <v>4.06</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>1.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.18</v>
+        <v>4.56</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="V7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.62</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AG7" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.99</v>
+        <v>1.16</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.61</v>
+        <v>4.06</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>1.71</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.18</v>
+        <v>4.56</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="V6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.62</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AG6" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.99</v>
+        <v>1.16</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.06</v>
+        <v>1.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.56</v>
+        <v>2.18</v>
       </c>
       <c r="R7" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="U7" t="n">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.05</v>
+        <v>4.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.16</v>
+        <v>1.99</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1198,17 +1198,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="O5" t="n">
         <v>4.5</v>
       </c>
       <c r="P5" t="n">
-        <v>5.81</v>
+        <v>4.35</v>
       </c>
       <c r="Q5" t="n">
         <v>1.83</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>4.23</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.06</v>
+        <v>1.61</v>
       </c>
       <c r="O6" t="n">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.71</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.56</v>
+        <v>2.18</v>
       </c>
       <c r="R6" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="U6" t="n">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.05</v>
+        <v>4.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.16</v>
+        <v>1.99</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.61</v>
+        <v>3.21</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.18</v>
+        <v>3.82</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="V7" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
         <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.85</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.99</v>
+        <v>1.27</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -725,16 +725,16 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="O2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P2" t="n">
         <v>3</v>
       </c>
-      <c r="P2" t="n">
-        <v>3.12</v>
-      </c>
       <c r="Q2" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="R2" t="n">
         <v>1.92</v>
@@ -776,13 +776,13 @@
         <v>1.15</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF2" t="n">
         <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,10 +884,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.23</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
         <v>1.8</v>
@@ -917,10 +917,10 @@
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA3" t="n">
         <v>2.09</v>
@@ -929,7 +929,7 @@
         <v>1.66</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AD3" t="n">
         <v>1.2</v>
@@ -938,7 +938,7 @@
         <v>1.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
         <v>1.77</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="O4" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="P4" t="n">
-        <v>3.3</v>
+        <v>4.02</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.7</v>
+        <v>1.98</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="O5" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
         <v>1.83</v>
@@ -1235,10 +1235,10 @@
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA5" t="n">
         <v>1.43</v>
@@ -1247,16 +1247,16 @@
         <v>2.73</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AE5" t="n">
         <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AG5" t="n">
         <v>2.25</v>
@@ -1370,13 +1370,13 @@
         <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T6" t="n">
         <v>3.55</v>
@@ -1388,7 +1388,7 @@
         <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
@@ -1397,22 +1397,22 @@
         <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AC6" t="n">
         <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF6" t="n">
         <v>1.51</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.61</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.11</v>
+        <v>4.25</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="S6" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="T6" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="V6" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.12</v>
+        <v>1.21</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.21</v>
+        <v>1.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.82</v>
+        <v>2.11</v>
       </c>
       <c r="R7" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="T7" t="n">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="U7" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
         <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.27</v>
+        <v>2.12</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1220,7 +1220,7 @@
         <v>1.2</v>
       </c>
       <c r="T5" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U5" t="n">
         <v>2.1</v>
@@ -1235,28 +1235,28 @@
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AB5" t="n">
         <v>2.73</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AE5" t="n">
         <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
         <v>2.25</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1364,10 +1364,10 @@
         <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P6" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
         <v>4.25</v>
@@ -1394,10 +1394,10 @@
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="AA6" t="n">
         <v>1.67</v>
@@ -1406,19 +1406,19 @@
         <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE6" t="n">
         <v>1.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O7" t="n">
         <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="Q7" t="n">
         <v>2.11</v>
@@ -1538,13 +1538,13 @@
         <v>1.23</v>
       </c>
       <c r="T7" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="V7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W7" t="n">
         <v>1.12</v>
@@ -1553,7 +1553,7 @@
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z7" t="n">
         <v>5</v>
@@ -1562,10 +1562,10 @@
         <v>1.44</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD7" t="n">
         <v>1.61</v>
@@ -1574,10 +1574,10 @@
         <v>1.22</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="Q2" t="n">
         <v>2.88</v>
@@ -749,7 +749,7 @@
         <v>3.25</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
@@ -770,13 +770,13 @@
         <v>1.54</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD2" t="n">
         <v>1.15</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF2" t="n">
         <v>1.95</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -890,13 +890,13 @@
         <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
         <v>5.12</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S3" t="n">
         <v>1.43</v>
@@ -917,10 +917,10 @@
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA3" t="n">
         <v>2.09</v>
@@ -935,13 +935,13 @@
         <v>1.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="O4" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="P4" t="n">
-        <v>4.02</v>
+        <v>3.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>4.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.25</v>
+        <v>2.11</v>
       </c>
       <c r="R6" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="S6" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="T6" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="U6" t="n">
-        <v>2.41</v>
+        <v>2.17</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.09</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.21</v>
+        <v>2.2</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P7" t="n">
-        <v>4.33</v>
+        <v>1.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.11</v>
+        <v>4.25</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="S7" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="T7" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="V7" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.2</v>
+        <v>1.21</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="O2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q2" t="n">
         <v>3</v>
       </c>
-      <c r="P2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.88</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="S2" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="T2" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="U2" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.56</v>
+        <v>2.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE2" t="n">
         <v>1.02</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK2" t="n">
         <v>1.52</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.12</v>
+        <v>5.07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>3.02</v>
+        <v>3.12</v>
       </c>
       <c r="V3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK3" t="n">
         <v>1.16</v>
@@ -1046,22 +1046,22 @@
         <v>1.95</v>
       </c>
       <c r="O4" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="P4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="S4" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U4" t="n">
         <v>3.58</v>
@@ -1073,34 +1073,34 @@
         <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE4" t="n">
         <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1205,25 +1205,25 @@
         <v>1.61</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="R5" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S5" t="n">
         <v>1.2</v>
       </c>
       <c r="T5" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="U5" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
         <v>1.71</v>
@@ -1238,28 +1238,28 @@
         <v>1.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="AC5" t="n">
         <v>2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="O6" t="n">
         <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>4.33</v>
+        <v>3.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="R6" t="n">
         <v>2.5</v>
       </c>
       <c r="S6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
         <v>3.42</v>
       </c>
       <c r="U6" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="V6" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="W6" t="n">
         <v>1.12</v>
@@ -1394,31 +1394,31 @@
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
         <v>5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
         <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,58 +1520,58 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="P7" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.25</v>
+        <v>4.14</v>
       </c>
       <c r="R7" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="S7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U7" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.09</v>
+        <v>3.91</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
         <v>1.57</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="O2" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="P2" t="n">
         <v>3.1</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.73</v>
+        <v>3.51</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="P6" t="n">
-        <v>3.92</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.09</v>
+        <v>4.14</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="S6" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="U6" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>5</v>
+        <v>3.91</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.17</v>
+        <v>2.87</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.51</v>
+        <v>1.73</v>
       </c>
       <c r="O7" t="n">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>1.87</v>
+        <v>3.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.14</v>
+        <v>2.09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="U7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AB7" t="n">
         <v>2.4</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AC7" t="n">
-        <v>2.87</v>
+        <v>2.17</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O5" t="n">
         <v>4.9</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.51</v>
+        <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>3.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.14</v>
+        <v>2.09</v>
       </c>
       <c r="R6" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="S6" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="U6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AB6" t="n">
         <v>2.4</v>
       </c>
-      <c r="V6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AC6" t="n">
-        <v>2.87</v>
+        <v>2.17</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.73</v>
+        <v>3.51</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="P7" t="n">
-        <v>3.92</v>
+        <v>1.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.09</v>
+        <v>4.14</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="S7" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="U7" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="Z7" t="n">
-        <v>5</v>
+        <v>3.91</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.17</v>
+        <v>2.87</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="O6" t="n">
         <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="Q6" t="n">
         <v>2.09</v>
@@ -1403,7 +1403,7 @@
         <v>1.49</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC6" t="n">
         <v>2.17</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.64</v>
+        <v>3.4</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>4.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.09</v>
+        <v>4.14</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="S6" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="U6" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>5</v>
+        <v>3.91</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.17</v>
+        <v>2.87</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.51</v>
+        <v>1.64</v>
       </c>
       <c r="O7" t="n">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>1.87</v>
+        <v>4.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.14</v>
+        <v>2.09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.91</v>
+        <v>5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.87</v>
+        <v>2.17</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="P2" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="O3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
         <v>5.07</v>
@@ -926,7 +926,7 @@
         <v>2.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC3" t="n">
         <v>3.95</v>
@@ -1049,7 +1049,7 @@
         <v>2.87</v>
       </c>
       <c r="P4" t="n">
-        <v>3.8</v>
+        <v>4.14</v>
       </c>
       <c r="Q4" t="n">
         <v>2.75</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -702,36 +702,36 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O2" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="P2" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
@@ -786,12 +786,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '74']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46176.54166666666</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="O3" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
         <v>5.07</v>
@@ -926,7 +926,7 @@
         <v>2.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC3" t="n">
         <v>3.95</v>
@@ -1049,7 +1049,7 @@
         <v>2.87</v>
       </c>
       <c r="P4" t="n">
-        <v>4.14</v>
+        <v>4.54</v>
       </c>
       <c r="Q4" t="n">
         <v>2.75</v>
@@ -1085,7 +1085,7 @@
         <v>2.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC4" t="n">
         <v>4.95</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="O5" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="P5" t="n">
-        <v>6.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q5" t="n">
         <v>2.15</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.4</v>
+        <v>3.07</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
         <v>4.14</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -873,14 +873,14 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74', '90+4']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46176.625</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O4" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>4.54</v>
+        <v>3.7</v>
       </c>
       <c r="Q4" t="n">
         <v>2.75</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.07</v>
+        <v>1.64</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>4.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.14</v>
+        <v>2.09</v>
       </c>
       <c r="R6" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="S6" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="U6" t="n">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.91</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.87</v>
+        <v>2.17</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.64</v>
+        <v>3.07</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>4.1</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.09</v>
+        <v>4.14</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="S7" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="U7" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="Z7" t="n">
-        <v>5</v>
+        <v>3.91</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.17</v>
+        <v>2.87</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-03.xlsx
+++ b/jogos_2026-06-03.xlsx
@@ -1023,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1035,11 +1035,11 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
@@ -1122,28 +1122,28 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46176.70833333334</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.64</v>
+        <v>3.07</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>4.1</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.09</v>
+        <v>4.14</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="S6" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="U6" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>5</v>
+        <v>3.91</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.17</v>
+        <v>2.87</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.07</v>
+        <v>1.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>4.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.14</v>
+        <v>2.09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.91</v>
+        <v>5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.87</v>
+        <v>2.17</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
